--- a/VerveStacks_POL_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD84E9AF-E6DD-4FB4-B542-7CC97EBFCF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A1EF9A6-1105-413D-B5F9-1643CC5743B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -852,28 +852,82 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_005</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 5</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_006</t>
@@ -888,22 +942,22 @@
     <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_011</t>
@@ -912,54 +966,6 @@
     <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_009</t>
   </si>
   <si>
@@ -972,25 +978,46 @@
     <t>connecting solar to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w111615226-220_POL</t>
+  </si>
+  <si>
+    <t>e_w111615226-220_POL,e_PL75-220_POL</t>
+  </si>
+  <si>
+    <t>e_w191035265-220_POL,e_w29115701-220_POL,e_PL17-400_POL</t>
+  </si>
+  <si>
+    <t>e_w39428977-400_POL,e_LT1-400_POL</t>
+  </si>
+  <si>
+    <t>e_w111615226-220_POL,e_PL75-220_POL,e_w293484891-220_POL</t>
+  </si>
+  <si>
+    <t>e_w293484891-220_POL,e_w86494356-400_POL,e_w29115701-220_POL</t>
+  </si>
+  <si>
+    <t>e_w293484891-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL75-220_POL,e_w133537926-220_POL,e_w191035265-220_POL</t>
+  </si>
+  <si>
+    <t>e_w29115701-220_POL,e_w293484891-220_POL</t>
+  </si>
+  <si>
+    <t>e_w255314292_POL</t>
+  </si>
+  <si>
     <t>e_w111615226-220_POL,e_w255314292_POL,e_w86494356-400_POL</t>
   </si>
   <si>
-    <t>e_PL75-220_POL,e_w133537926-220_POL,e_w191035265-220_POL</t>
-  </si>
-  <si>
-    <t>e_w29115701-220_POL,e_w293484891-220_POL</t>
+    <t>e_w86494356-400_POL,e_w39428977-400_POL</t>
   </si>
   <si>
     <t>e_w29115701-220_POL,e_w111615226-220_POL</t>
@@ -999,46 +1026,79 @@
     <t>e_w191035265-220_POL,e_PL17-400_POL</t>
   </si>
   <si>
-    <t>e_w39428977-400_POL,e_LT1-400_POL</t>
-  </si>
-  <si>
-    <t>e_w111615226-220_POL,e_PL75-220_POL,e_w293484891-220_POL</t>
-  </si>
-  <si>
-    <t>e_w293484891-220_POL,e_w86494356-400_POL,e_w29115701-220_POL</t>
+    <t>e_PL75-220_POL,e_w293484891-220_POL,e_w191035265-220_POL</t>
+  </si>
+  <si>
+    <t>e_w191035265-220_POL,e_w29115701-220_POL</t>
+  </si>
+  <si>
+    <t>e_w303870256-400_POL</t>
   </si>
   <si>
     <t>e_w303870256-400_POL,e_PL17-400_POL</t>
   </si>
   <si>
-    <t>e_w303870256-400_POL</t>
-  </si>
-  <si>
-    <t>e_w293484891-220_POL</t>
-  </si>
-  <si>
-    <t>e_w111615226-220_POL</t>
-  </si>
-  <si>
-    <t>e_w111615226-220_POL,e_PL75-220_POL</t>
-  </si>
-  <si>
-    <t>e_w191035265-220_POL,e_w29115701-220_POL,e_PL17-400_POL</t>
-  </si>
-  <si>
-    <t>e_w86494356-400_POL,e_w39428977-400_POL</t>
-  </si>
-  <si>
-    <t>e_PL75-220_POL,e_w293484891-220_POL,e_w191035265-220_POL</t>
-  </si>
-  <si>
-    <t>e_w191035265-220_POL,e_w29115701-220_POL</t>
-  </si>
-  <si>
     <t>e_PL17-400_POL,e_w29115701-220_POL</t>
   </si>
   <si>
-    <t>e_w255314292_POL</t>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_019</t>
@@ -1047,16 +1107,22 @@
     <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_014</t>
@@ -1071,40 +1137,16 @@
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_012</t>
@@ -1119,46 +1161,49 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>e_PL75-220_POL,e_w133537926-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>e_w191035265-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>e_w111615226-220_POL,e_w293484891-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>e_w29115701-220_POL,e_w303870256-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>e_w293484891-220_POL,e_w191035265-220_POL,e_w29115701-220_POL</t>
   </si>
   <si>
     <t>elc_won_POL_019</t>
@@ -1167,16 +1212,16 @@
     <t>e_w133537926-220_POL,e_w293484891-220_POL,e_w191035265-220_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>e_w111615226-220_POL,e_w293484891-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>e_w29115701-220_POL,e_w303870256-400_POL</t>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>e_w133537926-220_POL,e_w191035265-220_POL,e_w29115701-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_005</t>
   </si>
   <si>
     <t>elc_won_POL_014</t>
@@ -1188,28 +1233,13 @@
     <t>e_PL75-220_POL,e_w293484891-220_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>e_PL75-220_POL,e_w133537926-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>e_w191035265-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>elc_won_POL_010</t>
+  </si>
+  <si>
+    <t>e_w39428977-400_POL,e_LT1-400_POL,e_w255314292_POL,e_w86494356-400_POL</t>
   </si>
   <si>
     <t>elc_won_POL_012</t>
@@ -1224,36 +1254,6 @@
     <t>e_w29115701-220_POL,e_w293484891-220_POL,e_PL17-400_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>e_w133537926-220_POL,e_w191035265-220_POL,e_w29115701-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>elc_won_POL_010</t>
-  </si>
-  <si>
-    <t>e_w39428977-400_POL,e_LT1-400_POL,e_w255314292_POL,e_w86494356-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>e_w293484891-220_POL,e_w191035265-220_POL,e_w29115701-220_POL</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_POL_005</t>
   </si>
   <si>
@@ -1266,6 +1266,30 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_POL_008</t>
   </si>
   <si>
@@ -1278,24 +1302,6 @@
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_POL_004</t>
   </si>
   <si>
@@ -1308,12 +1314,6 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
     <t>elc_wof_POL_005</t>
   </si>
   <si>
@@ -1323,6 +1323,18 @@
     <t>elc_wof_POL_001</t>
   </si>
   <si>
+    <t>elc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_002</t>
+  </si>
+  <si>
     <t>elc_wof_POL_008</t>
   </si>
   <si>
@@ -1332,15 +1344,6 @@
     <t>elc_wof_POL_003</t>
   </si>
   <si>
-    <t>elc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_007</t>
-  </si>
-  <si>
     <t>elc_wof_POL_004</t>
   </si>
   <si>
@@ -1348,9 +1351,6 @@
   </si>
   <si>
     <t>elc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_009</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -6358,7 +6358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4532405F-4189-4AFE-9E85-3578630EA6EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0038B72B-FD86-421F-AA37-795D5DC718E1}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -6596,16 +6596,16 @@
         <v>241</v>
       </c>
       <c r="Y11" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="Z11" t="s">
         <v>285</v>
       </c>
       <c r="AA11">
-        <v>0.99729953359766199</v>
+        <v>0.99733507264559695</v>
       </c>
       <c r="AB11">
-        <v>49.508550709529651</v>
+        <v>48.857001497390002</v>
       </c>
       <c r="AD11" t="s">
         <v>240</v>
@@ -6635,13 +6635,13 @@
         <v>344</v>
       </c>
       <c r="AN11" t="s">
-        <v>345</v>
+        <v>286</v>
       </c>
       <c r="AO11">
-        <v>0.99873239758997023</v>
+        <v>0.99622969699231045</v>
       </c>
       <c r="AP11">
-        <v>23.239377517213022</v>
+        <v>69.122221807641537</v>
       </c>
       <c r="AR11" t="s">
         <v>240</v>
@@ -6742,16 +6742,16 @@
         <v>245</v>
       </c>
       <c r="Y12" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="Z12" t="s">
         <v>286</v>
       </c>
       <c r="AA12">
-        <v>0.99801094175818605</v>
+        <v>0.99583365539385327</v>
       </c>
       <c r="AB12">
-        <v>36.466067766588218</v>
+        <v>76.382984446022675</v>
       </c>
       <c r="AD12" t="s">
         <v>240</v>
@@ -6778,16 +6778,16 @@
         <v>306</v>
       </c>
       <c r="AM12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AN12" t="s">
-        <v>347</v>
+        <v>297</v>
       </c>
       <c r="AO12">
-        <v>0.99883902037019667</v>
+        <v>0.99653588726932718</v>
       </c>
       <c r="AP12">
-        <v>21.284626546395259</v>
+        <v>63.508733395668145</v>
       </c>
       <c r="AR12" t="s">
         <v>240</v>
@@ -6888,16 +6888,16 @@
         <v>247</v>
       </c>
       <c r="Y13" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Z13" t="s">
         <v>287</v>
       </c>
       <c r="AA13">
-        <v>0.99909366739195871</v>
+        <v>0.99875154162789404</v>
       </c>
       <c r="AB13">
-        <v>16.616097814091063</v>
+        <v>22.888403488609324</v>
       </c>
       <c r="AD13" t="s">
         <v>240</v>
@@ -6924,16 +6924,16 @@
         <v>308</v>
       </c>
       <c r="AM13" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AN13" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AO13">
-        <v>0.99521984547821263</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP13">
-        <v>87.636166232768815</v>
+        <v>65.760110609622657</v>
       </c>
       <c r="AR13" t="s">
         <v>240</v>
@@ -6963,13 +6963,13 @@
         <v>398</v>
       </c>
       <c r="BB13" t="s">
-        <v>399</v>
+        <v>294</v>
       </c>
       <c r="BC13">
-        <v>0.99383395234396599</v>
+        <v>0.99603343715055259</v>
       </c>
       <c r="BD13">
-        <v>113.04420702728957</v>
+        <v>72.720318906536249</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7034,16 +7034,16 @@
         <v>249</v>
       </c>
       <c r="Y14" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="Z14" t="s">
         <v>288</v>
       </c>
       <c r="AA14">
-        <v>0.99648087644372252</v>
+        <v>0.99812712894455979</v>
       </c>
       <c r="AB14">
-        <v>64.517265198419722</v>
+        <v>34.335969349736395</v>
       </c>
       <c r="AD14" t="s">
         <v>240</v>
@@ -7070,16 +7070,16 @@
         <v>310</v>
       </c>
       <c r="AM14" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AN14" t="s">
-        <v>285</v>
+        <v>349</v>
       </c>
       <c r="AO14">
-        <v>0.99730422320290779</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP14">
-        <v>49.422574613357185</v>
+        <v>100.87794092441324</v>
       </c>
       <c r="AR14" t="s">
         <v>240</v>
@@ -7106,16 +7106,16 @@
         <v>381</v>
       </c>
       <c r="BA14" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="BB14" t="s">
-        <v>396</v>
+        <v>294</v>
       </c>
       <c r="BC14">
-        <v>0.99564789206089888</v>
+        <v>0.99399718012600935</v>
       </c>
       <c r="BD14">
-        <v>79.788645550187297</v>
+        <v>110.05169768982766</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7180,16 +7180,16 @@
         <v>251</v>
       </c>
       <c r="Y15" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="Z15" t="s">
         <v>289</v>
       </c>
       <c r="AA15">
-        <v>0.99621535905375425</v>
+        <v>0.99834158364926728</v>
       </c>
       <c r="AB15">
-        <v>69.385084014505708</v>
+        <v>30.404299763434018</v>
       </c>
       <c r="AD15" t="s">
         <v>240</v>
@@ -7216,16 +7216,16 @@
         <v>312</v>
       </c>
       <c r="AM15" t="s">
+        <v>350</v>
+      </c>
+      <c r="AN15" t="s">
         <v>351</v>
       </c>
-      <c r="AN15" t="s">
-        <v>352</v>
-      </c>
       <c r="AO15">
-        <v>0.99805709209211746</v>
+        <v>0.99883902037019667</v>
       </c>
       <c r="AP15">
-        <v>35.619978311179104</v>
+        <v>21.284626546395259</v>
       </c>
       <c r="AR15" t="s">
         <v>240</v>
@@ -7252,10 +7252,10 @@
         <v>383</v>
       </c>
       <c r="BA15" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="BB15" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="BC15">
         <v>0.99609037037675463</v>
@@ -7326,16 +7326,16 @@
         <v>253</v>
       </c>
       <c r="Y16" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="Z16" t="s">
         <v>290</v>
       </c>
       <c r="AA16">
-        <v>0.99812712894455979</v>
+        <v>0.9987403722896917</v>
       </c>
       <c r="AB16">
-        <v>34.335969349736395</v>
+        <v>23.093174688985375</v>
       </c>
       <c r="AD16" t="s">
         <v>240</v>
@@ -7362,16 +7362,16 @@
         <v>314</v>
       </c>
       <c r="AM16" t="s">
+        <v>352</v>
+      </c>
+      <c r="AN16" t="s">
         <v>353</v>
       </c>
-      <c r="AN16" t="s">
-        <v>288</v>
-      </c>
       <c r="AO16">
-        <v>0.99653588726932718</v>
+        <v>0.99521984547821263</v>
       </c>
       <c r="AP16">
-        <v>63.508733395668145</v>
+        <v>87.636166232768815</v>
       </c>
       <c r="AR16" t="s">
         <v>240</v>
@@ -7398,7 +7398,7 @@
         <v>385</v>
       </c>
       <c r="BA16" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="BB16" t="s">
         <v>396</v>
@@ -7472,16 +7472,16 @@
         <v>255</v>
       </c>
       <c r="Y17" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="Z17" t="s">
         <v>291</v>
       </c>
       <c r="AA17">
-        <v>0.99834158364926728</v>
+        <v>0.99839233674974392</v>
       </c>
       <c r="AB17">
-        <v>30.404299763434018</v>
+        <v>29.473826254695162</v>
       </c>
       <c r="AD17" t="s">
         <v>240</v>
@@ -7511,13 +7511,13 @@
         <v>354</v>
       </c>
       <c r="AN17" t="s">
-        <v>355</v>
+        <v>296</v>
       </c>
       <c r="AO17">
-        <v>0.99641308487583879</v>
+        <v>0.99635146162488653</v>
       </c>
       <c r="AP17">
-        <v>65.760110609622657</v>
+        <v>66.889870210414614</v>
       </c>
       <c r="AR17" t="s">
         <v>240</v>
@@ -7544,16 +7544,16 @@
         <v>387</v>
       </c>
       <c r="BA17" t="s">
+        <v>402</v>
+      </c>
+      <c r="BB17" t="s">
         <v>403</v>
       </c>
-      <c r="BB17" t="s">
-        <v>303</v>
-      </c>
       <c r="BC17">
-        <v>0.99603343715055259</v>
+        <v>0.99383395234396599</v>
       </c>
       <c r="BD17">
-        <v>72.720318906536249</v>
+        <v>113.04420702728957</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7618,16 +7618,16 @@
         <v>257</v>
       </c>
       <c r="Y18" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Z18" t="s">
         <v>292</v>
       </c>
       <c r="AA18">
-        <v>0.9987403722896917</v>
+        <v>0.99801094175818605</v>
       </c>
       <c r="AB18">
-        <v>23.093174688985375</v>
+        <v>36.466067766588218</v>
       </c>
       <c r="AD18" t="s">
         <v>240</v>
@@ -7654,16 +7654,16 @@
         <v>318</v>
       </c>
       <c r="AM18" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AN18" t="s">
-        <v>357</v>
+        <v>298</v>
       </c>
       <c r="AO18">
-        <v>0.99449756685866841</v>
+        <v>0.99586212495478665</v>
       </c>
       <c r="AP18">
-        <v>100.87794092441324</v>
+        <v>75.861042495577635</v>
       </c>
       <c r="AR18" t="s">
         <v>240</v>
@@ -7693,13 +7693,13 @@
         <v>404</v>
       </c>
       <c r="BB18" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="BC18">
-        <v>0.99255696761939116</v>
+        <v>0.99564789206089888</v>
       </c>
       <c r="BD18">
-        <v>136.4555936444961</v>
+        <v>79.788645550187297</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7764,16 +7764,16 @@
         <v>259</v>
       </c>
       <c r="Y19" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="Z19" t="s">
         <v>293</v>
       </c>
       <c r="AA19">
-        <v>0.99692898913090644</v>
+        <v>0.99909366739195871</v>
       </c>
       <c r="AB19">
-        <v>56.301865933381954</v>
+        <v>16.616097814091063</v>
       </c>
       <c r="AD19" t="s">
         <v>240</v>
@@ -7800,16 +7800,16 @@
         <v>320</v>
       </c>
       <c r="AM19" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AN19" t="s">
-        <v>357</v>
+        <v>290</v>
       </c>
       <c r="AO19">
-        <v>0.99776911581804295</v>
+        <v>0.99826576737141715</v>
       </c>
       <c r="AP19">
-        <v>40.899543335879912</v>
+        <v>31.794264857351436</v>
       </c>
       <c r="AR19" t="s">
         <v>240</v>
@@ -7836,16 +7836,16 @@
         <v>391</v>
       </c>
       <c r="BA19" t="s">
+        <v>405</v>
+      </c>
+      <c r="BB19" t="s">
         <v>406</v>
       </c>
-      <c r="BB19" t="s">
-        <v>396</v>
-      </c>
       <c r="BC19">
-        <v>0.99615776238359954</v>
+        <v>0.99255696761939116</v>
       </c>
       <c r="BD19">
-        <v>70.441022967342263</v>
+        <v>136.4555936444961</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -7910,16 +7910,16 @@
         <v>261</v>
       </c>
       <c r="Y20" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Z20" t="s">
         <v>294</v>
       </c>
       <c r="AA20">
-        <v>0.99511607748745434</v>
+        <v>0.99763459325217896</v>
       </c>
       <c r="AB20">
-        <v>89.538579396670116</v>
+        <v>43.365790376719588</v>
       </c>
       <c r="AD20" t="s">
         <v>240</v>
@@ -7946,16 +7946,16 @@
         <v>322</v>
       </c>
       <c r="AM20" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AN20" t="s">
-        <v>299</v>
+        <v>358</v>
       </c>
       <c r="AO20">
-        <v>0.99635146162488653</v>
+        <v>0.99871360797890252</v>
       </c>
       <c r="AP20">
-        <v>66.889870210414614</v>
+        <v>23.583853720120768</v>
       </c>
       <c r="AR20" t="s">
         <v>240</v>
@@ -7985,13 +7985,13 @@
         <v>407</v>
       </c>
       <c r="BB20" t="s">
-        <v>303</v>
+        <v>396</v>
       </c>
       <c r="BC20">
-        <v>0.99399718012600935</v>
+        <v>0.99615776238359954</v>
       </c>
       <c r="BD20">
-        <v>110.05169768982766</v>
+        <v>70.441022967342263</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8056,16 +8056,16 @@
         <v>263</v>
       </c>
       <c r="Y21" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="Z21" t="s">
         <v>295</v>
       </c>
       <c r="AA21">
-        <v>0.99839233674974392</v>
+        <v>0.99729953359766199</v>
       </c>
       <c r="AB21">
-        <v>29.473826254695162</v>
+        <v>49.508550709529651</v>
       </c>
       <c r="AD21" t="s">
         <v>240</v>
@@ -8092,16 +8092,16 @@
         <v>324</v>
       </c>
       <c r="AM21" t="s">
+        <v>359</v>
+      </c>
+      <c r="AN21" t="s">
         <v>360</v>
       </c>
-      <c r="AN21" t="s">
-        <v>289</v>
-      </c>
       <c r="AO21">
-        <v>0.99586212495478665</v>
+        <v>0.99873239758997023</v>
       </c>
       <c r="AP21">
-        <v>75.861042495577635</v>
+        <v>23.239377517213022</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8166,16 +8166,16 @@
         <v>265</v>
       </c>
       <c r="Y22" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="Z22" t="s">
         <v>296</v>
       </c>
       <c r="AA22">
-        <v>0.99733507264559695</v>
+        <v>0.99738245649758195</v>
       </c>
       <c r="AB22">
-        <v>48.857001497390002</v>
+        <v>47.988297544331637</v>
       </c>
       <c r="AD22" t="s">
         <v>240</v>
@@ -8205,13 +8205,13 @@
         <v>361</v>
       </c>
       <c r="AN22" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="AO22">
-        <v>0.99749126227646956</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP22">
-        <v>45.993524931390482</v>
+        <v>40.899543335879912</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8276,16 +8276,16 @@
         <v>267</v>
       </c>
       <c r="Y23" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Z23" t="s">
         <v>297</v>
       </c>
       <c r="AA23">
-        <v>0.99583365539385327</v>
+        <v>0.99648087644372252</v>
       </c>
       <c r="AB23">
-        <v>76.382984446022675</v>
+        <v>64.517265198419722</v>
       </c>
       <c r="AD23" t="s">
         <v>240</v>
@@ -8312,16 +8312,16 @@
         <v>328</v>
       </c>
       <c r="AM23" t="s">
+        <v>362</v>
+      </c>
+      <c r="AN23" t="s">
         <v>363</v>
       </c>
-      <c r="AN23" t="s">
-        <v>364</v>
-      </c>
       <c r="AO23">
-        <v>0.99807543246352515</v>
+        <v>0.99845079995590791</v>
       </c>
       <c r="AP23">
-        <v>35.283738168705199</v>
+        <v>28.402000808355538</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8386,16 +8386,16 @@
         <v>269</v>
       </c>
       <c r="Y24" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="Z24" t="s">
         <v>298</v>
       </c>
       <c r="AA24">
-        <v>0.99875154162789404</v>
+        <v>0.99621535905375425</v>
       </c>
       <c r="AB24">
-        <v>22.888403488609324</v>
+        <v>69.385084014505708</v>
       </c>
       <c r="AD24" t="s">
         <v>240</v>
@@ -8422,16 +8422,16 @@
         <v>330</v>
       </c>
       <c r="AM24" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AN24" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AO24">
-        <v>0.99622969699231045</v>
+        <v>0.9963019969989696</v>
       </c>
       <c r="AP24">
-        <v>69.122221807641537</v>
+        <v>67.796721685557472</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8496,16 +8496,16 @@
         <v>271</v>
       </c>
       <c r="Y25" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="Z25" t="s">
         <v>299</v>
       </c>
       <c r="AA25">
-        <v>0.99738245649758195</v>
+        <v>0.99860106452186825</v>
       </c>
       <c r="AB25">
-        <v>47.988297544331637</v>
+        <v>25.647150432415483</v>
       </c>
       <c r="AD25" t="s">
         <v>240</v>
@@ -8532,16 +8532,16 @@
         <v>332</v>
       </c>
       <c r="AM25" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AN25" t="s">
-        <v>367</v>
+        <v>295</v>
       </c>
       <c r="AO25">
-        <v>0.99845079995590791</v>
+        <v>0.99730422320290779</v>
       </c>
       <c r="AP25">
-        <v>28.402000808355538</v>
+        <v>49.422574613357185</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8606,16 +8606,16 @@
         <v>273</v>
       </c>
       <c r="Y26" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Z26" t="s">
         <v>300</v>
       </c>
       <c r="AA26">
-        <v>0.99860106452186825</v>
+        <v>0.99775856069920277</v>
       </c>
       <c r="AB26">
-        <v>25.647150432415483</v>
+        <v>41.093053847949164</v>
       </c>
       <c r="AD26" t="s">
         <v>240</v>
@@ -8642,16 +8642,16 @@
         <v>334</v>
       </c>
       <c r="AM26" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AN26" t="s">
-        <v>293</v>
+        <v>367</v>
       </c>
       <c r="AO26">
-        <v>0.9963019969989696</v>
+        <v>0.99805709209211746</v>
       </c>
       <c r="AP26">
-        <v>67.796721685557472</v>
+        <v>35.619978311179104</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8716,16 +8716,16 @@
         <v>275</v>
       </c>
       <c r="Y27" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="Z27" t="s">
         <v>301</v>
       </c>
       <c r="AA27">
-        <v>0.99775856069920277</v>
+        <v>0.99511607748745434</v>
       </c>
       <c r="AB27">
-        <v>41.093053847949164</v>
+        <v>89.538579396670116</v>
       </c>
       <c r="AD27" t="s">
         <v>240</v>
@@ -8752,10 +8752,10 @@
         <v>336</v>
       </c>
       <c r="AM27" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AN27" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="AO27">
         <v>0.99802303154782224</v>
@@ -8826,16 +8826,16 @@
         <v>277</v>
       </c>
       <c r="Y28" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Z28" t="s">
         <v>302</v>
       </c>
       <c r="AA28">
-        <v>0.99572127940552169</v>
+        <v>0.99692898913090644</v>
       </c>
       <c r="AB28">
-        <v>78.443210898768598</v>
+        <v>56.301865933381954</v>
       </c>
       <c r="AD28" t="s">
         <v>240</v>
@@ -8862,10 +8862,10 @@
         <v>338</v>
       </c>
       <c r="AM28" t="s">
+        <v>369</v>
+      </c>
+      <c r="AN28" t="s">
         <v>370</v>
-      </c>
-      <c r="AN28" t="s">
-        <v>371</v>
       </c>
       <c r="AO28">
         <v>0.99714358927215652</v>
@@ -8936,16 +8936,16 @@
         <v>279</v>
       </c>
       <c r="Y29" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="Z29" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="AA29">
-        <v>0.99505524223378883</v>
+        <v>0.99572127940552169</v>
       </c>
       <c r="AB29">
-        <v>90.653892380538664</v>
+        <v>78.443210898768598</v>
       </c>
       <c r="AD29" t="s">
         <v>240</v>
@@ -8972,16 +8972,16 @@
         <v>340</v>
       </c>
       <c r="AM29" t="s">
+        <v>371</v>
+      </c>
+      <c r="AN29" t="s">
         <v>372</v>
       </c>
-      <c r="AN29" t="s">
-        <v>292</v>
-      </c>
       <c r="AO29">
-        <v>0.99826576737141715</v>
+        <v>0.99749126227646956</v>
       </c>
       <c r="AP29">
-        <v>31.794264857351436</v>
+        <v>45.993524931390482</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9046,16 +9046,16 @@
         <v>281</v>
       </c>
       <c r="Y30" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="Z30" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="AA30">
-        <v>0.99763459325217896</v>
+        <v>0.99505524223378883</v>
       </c>
       <c r="AB30">
-        <v>43.365790376719588</v>
+        <v>90.653892380538664</v>
       </c>
       <c r="AD30" t="s">
         <v>240</v>
@@ -9088,10 +9088,10 @@
         <v>374</v>
       </c>
       <c r="AO30">
-        <v>0.99871360797890252</v>
+        <v>0.99807543246352515</v>
       </c>
       <c r="AP30">
-        <v>23.583853720120768</v>
+        <v>35.283738168705199</v>
       </c>
     </row>
   </sheetData>
@@ -9100,7 +9100,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46C5ABCE-E73E-4059-94AA-C855A02488C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{846CF8C5-CC92-4D59-9CBD-BD33E3AD0430}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -9212,7 +9212,7 @@
         <v>408</v>
       </c>
       <c r="K11" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="L11">
         <v>0.30278350605008381</v>
@@ -9280,7 +9280,7 @@
         <v>410</v>
       </c>
       <c r="K12" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="L12">
         <v>0.44035497786033617</v>
@@ -9313,7 +9313,7 @@
         <v>450</v>
       </c>
       <c r="X12" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -9348,7 +9348,7 @@
         <v>412</v>
       </c>
       <c r="K13" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="L13">
         <v>1.6077871713950227</v>
@@ -9381,7 +9381,7 @@
         <v>452</v>
       </c>
       <c r="X13" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -9416,7 +9416,7 @@
         <v>414</v>
       </c>
       <c r="K14" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="L14">
         <v>2.531891424764753</v>
@@ -9449,7 +9449,7 @@
         <v>454</v>
       </c>
       <c r="X14" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -9484,7 +9484,7 @@
         <v>416</v>
       </c>
       <c r="K15" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="L15">
         <v>7.6497810049421515</v>
@@ -9552,7 +9552,7 @@
         <v>418</v>
       </c>
       <c r="K16" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="L16">
         <v>0.63333325583919986</v>
@@ -9585,7 +9585,7 @@
         <v>458</v>
       </c>
       <c r="X16" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Y16">
         <v>8.8230000000000004</v>
@@ -9620,7 +9620,7 @@
         <v>420</v>
       </c>
       <c r="K17" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="L17">
         <v>0.78389041837100704</v>
@@ -9653,7 +9653,7 @@
         <v>460</v>
       </c>
       <c r="X17" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="Y17">
         <v>0.22650000000000001</v>
@@ -9688,7 +9688,7 @@
         <v>422</v>
       </c>
       <c r="K18" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="L18">
         <v>3.0365724666245324</v>
@@ -9721,7 +9721,7 @@
         <v>462</v>
       </c>
       <c r="X18" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -9756,7 +9756,7 @@
         <v>424</v>
       </c>
       <c r="K19" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="L19">
         <v>0.22970161230087291</v>
@@ -9789,7 +9789,7 @@
         <v>464</v>
       </c>
       <c r="X19" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="Y19">
         <v>13.37175</v>
@@ -9824,7 +9824,7 @@
         <v>426</v>
       </c>
       <c r="K20" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="L20">
         <v>0.27066515065379043</v>
@@ -9857,7 +9857,7 @@
         <v>466</v>
       </c>
       <c r="X20" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Y20">
         <v>3.9427500000000002</v>
@@ -9892,7 +9892,7 @@
         <v>428</v>
       </c>
       <c r="K21" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="L21">
         <v>0.32193208719379746</v>
@@ -9927,7 +9927,7 @@
         <v>430</v>
       </c>
       <c r="K22" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="L22">
         <v>0.6573344927201471</v>
@@ -9962,7 +9962,7 @@
         <v>432</v>
       </c>
       <c r="K23" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="L23">
         <v>0.28992997651770519</v>
@@ -9997,7 +9997,7 @@
         <v>434</v>
       </c>
       <c r="K24" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="L24">
         <v>0.74609319967150689</v>
@@ -10032,7 +10032,7 @@
         <v>436</v>
       </c>
       <c r="K25" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -10067,7 +10067,7 @@
         <v>438</v>
       </c>
       <c r="K26" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="L26">
         <v>0.7924639655878376</v>
@@ -10102,7 +10102,7 @@
         <v>440</v>
       </c>
       <c r="K27" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -10137,7 +10137,7 @@
         <v>442</v>
       </c>
       <c r="K28" t="s">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="L28">
         <v>1.4327274230737423</v>
@@ -10172,7 +10172,7 @@
         <v>444</v>
       </c>
       <c r="K29" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="L29">
         <v>0.58742801517356968</v>
@@ -10207,7 +10207,7 @@
         <v>446</v>
       </c>
       <c r="K30" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="L30">
         <v>0.35405891742987328</v>
@@ -10222,7 +10222,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0A64DB2-4601-44CD-BA2E-819CEF05B272}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5892102C-9BCB-4C30-98DF-731A42396D7C}">
   <dimension ref="B9:S128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
